--- a/Employee_Reports_wi48/Ronnie Villanueva Gutierrez Q0314.xlsx
+++ b/Employee_Reports_wi48/Ronnie Villanueva Gutierrez Q0314.xlsx
@@ -548,11 +548,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -585,11 +585,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
